--- a/part2_kpi_experiment/outputs/experiment_summary.xlsx
+++ b/part2_kpi_experiment/outputs/experiment_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mitali Kalburgi\OneDrive\Desktop\Bitsom Notes\Assignments\Final Capstone Project\part2_kpi_experiment\part2_kpi_experiment\outputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EA9714A-A033-4DE5-9DDC-4C069C2B459C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D7EB065-F930-4CC2-8CC6-8AAB6EEC565F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" activeTab="1" xr2:uid="{D83E48A9-ED42-4144-A3CD-2D2CC2263F28}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="16800" windowHeight="9670" xr2:uid="{D83E48A9-ED42-4144-A3CD-2D2CC2263F28}"/>
   </bookViews>
   <sheets>
     <sheet name="experiment_dataset" sheetId="2" r:id="rId1"/>
@@ -4453,7 +4453,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4461,60 +4461,344 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="11">
+  <dxfs count="20">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right/>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
+      </border>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Carlito"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF155E75"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -4530,69 +4814,69 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2141F3BC-ABB0-4B3E-8F30-A6666D30011E}" name="Table1" displayName="Table1" ref="A3:C14" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2141F3BC-ABB0-4B3E-8F30-A6666D30011E}" name="Table1" displayName="Table1" ref="A3:C14" totalsRowShown="0" headerRowDxfId="19">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{B5FCBAAD-AC08-4ABC-8332-D96C3503D06E}" name="Metric" dataDxfId="10"/>
-    <tableColumn id="2" xr3:uid="{B67CB5DB-C933-40A3-83AC-C138A3B163B2}" name="Control" dataDxfId="9">
+    <tableColumn id="1" xr3:uid="{B5FCBAAD-AC08-4ABC-8332-D96C3503D06E}" name="Metric" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{B67CB5DB-C933-40A3-83AC-C138A3B163B2}" name="Control" dataDxfId="13">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C2:C1409,"Control")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A88464E6-594D-41D7-A948-89F448CD2004}" name="Treatment" dataDxfId="8">
+    <tableColumn id="3" xr3:uid="{A88464E6-594D-41D7-A948-89F448CD2004}" name="Treatment" dataDxfId="12">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C2:C1409,"Treatment")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8DEF158D-D94A-457F-A3CD-A41C3FC5E676}" name="Table2" displayName="Table2" ref="A20:C24" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{8DEF158D-D94A-457F-A3CD-A41C3FC5E676}" name="Table2" displayName="Table2" ref="A20:C24" totalsRowShown="0" headerRowDxfId="18">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{305DF5D4-A0EB-4CD9-AF36-E8145E91FBF0}" name="Region"/>
-    <tableColumn id="2" xr3:uid="{22761DDF-FED5-489A-9A16-EF3D4B699C4B}" name="Control" dataDxfId="7">
+    <tableColumn id="1" xr3:uid="{305DF5D4-A0EB-4CD9-AF36-E8145E91FBF0}" name="Region" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{22761DDF-FED5-489A-9A16-EF3D4B699C4B}" name="Control" dataDxfId="10">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"North",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"North")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{A87040B1-BFBC-4C63-AFD1-09418B8327B7}" name="Treatment" dataDxfId="6">
+    <tableColumn id="3" xr3:uid="{A87040B1-BFBC-4C63-AFD1-09418B8327B7}" name="Treatment" dataDxfId="9">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"North",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"North")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D156F55F-DE71-420D-9A1A-DC9A0709E9C0}" name="Table3" displayName="Table3" ref="F20:H23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{D156F55F-DE71-420D-9A1A-DC9A0709E9C0}" name="Table3" displayName="Table3" ref="F20:H23" totalsRowShown="0" headerRowDxfId="17">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{433C74AA-F070-4F03-8C67-B6CF227856E3}" name="Device Type"/>
-    <tableColumn id="2" xr3:uid="{47E9E7CC-91A0-424B-8BFD-66C8F48CAC73}" name="Control" dataDxfId="5">
+    <tableColumn id="1" xr3:uid="{433C74AA-F070-4F03-8C67-B6CF227856E3}" name="Device Type" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{47E9E7CC-91A0-424B-8BFD-66C8F48CAC73}" name="Control" dataDxfId="7">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Mobile",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Mobile")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{40DFAE03-3515-48EF-AB15-6C3E46A7CBCA}" name="Treatment" dataDxfId="4">
+    <tableColumn id="3" xr3:uid="{40DFAE03-3515-48EF-AB15-6C3E46A7CBCA}" name="Treatment" dataDxfId="6">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Mobile",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Mobile")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DC59F2DF-4EA8-4426-A500-0FC81DDA5B26}" name="Table4" displayName="Table4" ref="K20:M25" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{DC59F2DF-4EA8-4426-A500-0FC81DDA5B26}" name="Table4" displayName="Table4" ref="K20:M25" totalsRowShown="0" headerRowDxfId="16">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{1BFA637E-01A7-4AEB-A057-21E3F3F74349}" name="Traffic Source"/>
-    <tableColumn id="2" xr3:uid="{E2B262FB-F254-45BA-A060-9177E0B613B4}" name="Control" dataDxfId="3">
+    <tableColumn id="1" xr3:uid="{1BFA637E-01A7-4AEB-A057-21E3F3F74349}" name="Traffic Source" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{E2B262FB-F254-45BA-A060-9177E0B613B4}" name="Control" dataDxfId="4">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Organic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Organic")</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{269FF712-5C64-4C53-80E5-91360705DB44}" name="Treatment" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{269FF712-5C64-4C53-80E5-91360705DB44}" name="Treatment" dataDxfId="3">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Organic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Organic")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{23C1722C-D3D9-4157-A101-1AED9BE64BF0}" name="Table5" displayName="Table5" ref="Q20:S23" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{23C1722C-D3D9-4157-A101-1AED9BE64BF0}" name="Table5" displayName="Table5" ref="Q20:S23" totalsRowShown="0" headerRowDxfId="15">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0229C157-AB93-4324-9C3A-5EF4C0FB5B21}" name="Plan Type"/>
+    <tableColumn id="1" xr3:uid="{0229C157-AB93-4324-9C3A-5EF4C0FB5B21}" name="Plan Type" dataDxfId="2"/>
     <tableColumn id="2" xr3:uid="{59FC5FF6-8992-48D8-9C5A-F475194560AF}" name="Control" dataDxfId="1">
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Free",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Free")</calculatedColumnFormula>
     </tableColumn>
@@ -4600,7 +4884,7 @@
       <calculatedColumnFormula>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Free",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Free")</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
-  <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -70983,8 +71267,11 @@
     <col min="7" max="7" width="12.90625" customWidth="1"/>
     <col min="8" max="8" width="11.7265625" customWidth="1"/>
     <col min="11" max="11" width="12.6328125" customWidth="1"/>
-    <col min="12" max="13" width="10.453125" customWidth="1"/>
-    <col min="17" max="19" width="9.7265625" customWidth="1"/>
+    <col min="12" max="12" width="10.453125" customWidth="1"/>
+    <col min="13" max="13" width="12.90625" customWidth="1"/>
+    <col min="16" max="16" width="13.453125" customWidth="1"/>
+    <col min="17" max="18" width="9.7265625" customWidth="1"/>
+    <col min="19" max="19" width="14.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="23.5">
@@ -70993,13 +71280,13 @@
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>3</v>
       </c>
     </row>
@@ -71007,11 +71294,11 @@
       <c r="A4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="5">
         <f>COUNTIFS(experiment_dataset!C2:C1409,"Control")</f>
         <v>690</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="5">
         <f>COUNTIFS(experiment_dataset!C2:C1409,"Treatment")</f>
         <v>710</v>
       </c>
@@ -71020,11 +71307,11 @@
       <c r="A5" s="4" t="s">
         <v>1437</v>
       </c>
-      <c r="B5" s="5">
+      <c r="B5" s="6">
         <f>COUNTIFS(experiment_dataset!C2:C1409,"Control",experiment_dataset!H2:H1409,1)/experiment_summary!B4</f>
         <v>0.63623188405797104</v>
       </c>
-      <c r="C5" s="5">
+      <c r="C5" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!H:H,1)/C4</f>
         <v>0.72394366197183102</v>
       </c>
@@ -71033,11 +71320,11 @@
       <c r="A6" s="4" t="s">
         <v>1438</v>
       </c>
-      <c r="B6" s="5">
+      <c r="B6" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!I:I,1)/B4</f>
         <v>0.25072463768115943</v>
       </c>
-      <c r="C6" s="5">
+      <c r="C6" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!I:I,1)/C4</f>
         <v>0.29014084507042254</v>
       </c>
@@ -71046,11 +71333,11 @@
       <c r="A7" s="4" t="s">
         <v>1439</v>
       </c>
-      <c r="B7" s="5">
+      <c r="B7" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!J:J,1)/B4</f>
         <v>0.15652173913043479</v>
       </c>
-      <c r="C7" s="5">
+      <c r="C7" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!J:J,1)/C4</f>
         <v>0.21126760563380281</v>
       </c>
@@ -71059,11 +71346,11 @@
       <c r="A8" s="4" t="s">
         <v>1440</v>
       </c>
-      <c r="B8" s="5">
+      <c r="B8" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!K:K,1)/B4</f>
         <v>3.1884057971014491E-2</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C8" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!K:K,1)/C4</f>
         <v>7.0422535211267609E-2</v>
       </c>
@@ -71072,11 +71359,11 @@
       <c r="A9" s="4" t="s">
         <v>1441</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="7">
         <f>SUMIF(experiment_dataset!C:C,"Control",experiment_dataset!L:L)/B4</f>
         <v>51.974318840579706</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="7">
         <f>SUMIF(experiment_dataset!C:C,"Treatment",experiment_dataset!L:L)/C4</f>
         <v>54.254521126760551</v>
       </c>
@@ -71085,11 +71372,11 @@
       <c r="A10" s="4" t="s">
         <v>1442</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="7">
         <f>SUMIF(experiment_dataset!C:C,"Control",experiment_dataset!L:L)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!K:K,1)</f>
         <v>1630.1036363636363</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="7">
         <f>SUMIF(experiment_dataset!C:C,"Treatment",experiment_dataset!L:L)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!K:K,1)</f>
         <v>770.41419999999982</v>
       </c>
@@ -71098,11 +71385,11 @@
       <c r="A11" s="4" t="s">
         <v>1443</v>
       </c>
-      <c r="B11" s="5">
+      <c r="B11" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!N:N,1)/B4</f>
         <v>0</v>
       </c>
-      <c r="C11" s="5">
+      <c r="C11" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!N:N,1)/C4</f>
         <v>4.2253521126760559E-3</v>
       </c>
@@ -71111,11 +71398,11 @@
       <c r="A12" s="4" t="s">
         <v>1444</v>
       </c>
-      <c r="B12" s="5">
+      <c r="B12" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!M:M,"&gt;"&amp;0)/B4</f>
         <v>0.14782608695652175</v>
       </c>
-      <c r="C12" s="5">
+      <c r="C12" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!M:M,"&gt;"&amp;0)/C4</f>
         <v>0.24788732394366197</v>
       </c>
@@ -71124,11 +71411,11 @@
       <c r="A13" s="4" t="s">
         <v>1445</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="7">
         <f>AVERAGEIF(experiment_dataset!C:C,"Control",experiment_dataset!P:P)</f>
         <v>57.029532163742729</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="7">
         <f>AVERAGEIF(experiment_dataset!C:C,"Treatment",experiment_dataset!P:P)</f>
         <v>62.940028490028489</v>
       </c>
@@ -71137,11 +71424,11 @@
       <c r="A14" s="4" t="s">
         <v>1446</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14" s="7">
         <f>AVERAGEIFS(experiment_dataset!O:O,experiment_dataset!C:C,"Control",experiment_dataset!K:K,1)</f>
         <v>8.8636363636363633</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="7">
         <f>AVERAGEIFS(experiment_dataset!O:O,experiment_dataset!C:C,"Treatment",experiment_dataset!K:K,1)</f>
         <v>6.4</v>
       </c>
@@ -71177,215 +71464,215 @@
       <c r="T18" s="1"/>
       <c r="U18" s="1"/>
     </row>
-    <row r="20" spans="1:21">
-      <c r="A20" t="s">
+    <row r="20" spans="1:21" ht="31" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>1448</v>
       </c>
-      <c r="B20" t="s">
-        <v>2</v>
-      </c>
-      <c r="C20" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" t="s">
+      <c r="B20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>1449</v>
       </c>
-      <c r="G20" t="s">
-        <v>2</v>
-      </c>
-      <c r="H20" t="s">
-        <v>3</v>
-      </c>
-      <c r="K20" t="s">
+      <c r="G20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="K20" s="2" t="s">
         <v>1453</v>
       </c>
-      <c r="L20" t="s">
-        <v>2</v>
-      </c>
-      <c r="M20" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" t="s">
+      <c r="L20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="M20" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>1455</v>
       </c>
-      <c r="R20" t="s">
-        <v>2</v>
-      </c>
-      <c r="S20" t="s">
+      <c r="R20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:21">
-      <c r="A21" t="s">
+      <c r="A21" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="5">
+      <c r="B21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"North",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"North")</f>
         <v>3.482587064676617E-2</v>
       </c>
-      <c r="C21" s="5">
+      <c r="C21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"North",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"North")</f>
         <v>8.8888888888888892E-2</v>
       </c>
-      <c r="F21" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Mobile",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Mobile")</f>
         <v>2.5821596244131457E-2</v>
       </c>
-      <c r="H21" s="5">
+      <c r="H21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Mobile",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Mobile")</f>
         <v>7.407407407407407E-2</v>
       </c>
-      <c r="K21" t="s">
+      <c r="K21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Organic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Organic")</f>
         <v>2.032520325203252E-2</v>
       </c>
-      <c r="M21" s="5">
+      <c r="M21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Organic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Organic")</f>
         <v>6.3291139240506333E-2</v>
       </c>
-      <c r="Q21" t="s">
-        <v>16</v>
-      </c>
-      <c r="R21" s="5">
+      <c r="Q21" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="R21" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Free",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Free")</f>
         <v>3.0555555555555555E-2</v>
       </c>
-      <c r="S21" s="7">
+      <c r="S21" s="8">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Free",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Free")</f>
         <v>9.2896174863387984E-2</v>
       </c>
     </row>
     <row r="22" spans="1:21">
-      <c r="A22" t="s">
+      <c r="A22" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="B22" s="5">
+      <c r="B22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"South",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"South")</f>
         <v>3.2608695652173912E-2</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"South",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"South")</f>
         <v>7.650273224043716E-2</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F22" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Desktop",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Desktop")</f>
         <v>4.4999999999999998E-2</v>
       </c>
-      <c r="H22" s="5">
+      <c r="H22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Desktop",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Desktop")</f>
         <v>6.5727699530516437E-2</v>
       </c>
-      <c r="K22" t="s">
+      <c r="K22" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Paid Search",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Paid Search")</f>
         <v>1.2903225806451613E-2</v>
       </c>
-      <c r="M22" s="5">
+      <c r="M22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Paid Search",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Paid Search")</f>
         <v>6.25E-2</v>
       </c>
-      <c r="Q22" t="s">
+      <c r="Q22" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="R22" s="5">
+      <c r="R22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Basic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Basic")</f>
         <v>3.6199095022624438E-2</v>
       </c>
-      <c r="S22" s="5">
+      <c r="S22" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Basic",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Basic")</f>
         <v>3.8793103448275863E-2</v>
       </c>
     </row>
     <row r="23" spans="1:21">
-      <c r="A23" t="s">
+      <c r="A23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B23" s="5">
+      <c r="B23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"East",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"East")</f>
         <v>2.5477707006369428E-2</v>
       </c>
-      <c r="C23" s="5">
+      <c r="C23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"East",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"East")</f>
         <v>6.4705882352941183E-2</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Tablet",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!E:E,"Tablet")</f>
         <v>1.8181818181818181E-2</v>
       </c>
-      <c r="H23" s="5">
+      <c r="H23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Tablet",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!E:E,"Tablet")</f>
         <v>7.1428571428571425E-2</v>
       </c>
-      <c r="K23" t="s">
+      <c r="K23" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Social",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Social")</f>
         <v>7.7519379844961239E-2</v>
       </c>
-      <c r="M23" s="5">
+      <c r="M23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Social",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Social")</f>
         <v>6.0606060606060608E-2</v>
       </c>
-      <c r="Q23" t="s">
+      <c r="Q23" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="R23" s="5">
+      <c r="R23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Premium",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!G:G,"Premium")</f>
         <v>2.7522935779816515E-2</v>
       </c>
-      <c r="S23" s="5">
+      <c r="S23" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Premium",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!G:G,"Premium")</f>
         <v>6.25E-2</v>
       </c>
     </row>
     <row r="24" spans="1:21">
-      <c r="A24" t="s">
+      <c r="A24" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="B24" s="5">
+      <c r="B24" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"West",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!D:D,"West")</f>
         <v>3.3783783783783786E-2</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"West",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!D:D,"West")</f>
         <v>5.0847457627118647E-2</v>
       </c>
-      <c r="K24" t="s">
+      <c r="K24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Referral",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Referral")</f>
         <v>2.4691358024691357E-2</v>
       </c>
-      <c r="M24" s="5">
+      <c r="M24" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Referral",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Referral")</f>
         <v>0.10989010989010989</v>
       </c>
     </row>
     <row r="25" spans="1:21">
-      <c r="K25" t="s">
+      <c r="K25" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="L25" s="5">
+      <c r="L25" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Email",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Control",experiment_dataset!F:F,"Email")</f>
         <v>2.7397260273972601E-2</v>
       </c>
-      <c r="M25" s="5">
+      <c r="M25" s="6">
         <f>COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Email",experiment_dataset!K:K,1)/COUNTIFS(experiment_dataset!C:C,"Treatment",experiment_dataset!F:F,"Email")</f>
         <v>7.1428571428571425E-2</v>
       </c>
